--- a/human_resources_forms/015_employee_exit_check_out_form--human_resources_forms.xlsx
+++ b/human_resources_forms/015_employee_exit_check_out_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_before_departure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Title Before Departure</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>date_of_departure</t>
+          <t>reason_for_departure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>date_of_departure</t>
+          <t>Reason for Departure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reason_for_departure</t>
+          <t>manager_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reason_for_departure</t>
+          <t>Manager Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_title_before_departure</t>
+          <t>manager_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>job_title_before_departure</t>
+          <t>Manager Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_title_after_departure</t>
+          <t>manager_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>job_title_after_departure</t>
+          <t>Manager Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,46 +676,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>manager_phone</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>manager_phone</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manager_email</t>
+          <t>supervisor_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manager_email</t>
+          <t>Supervisor Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>supervisor_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Supervisor Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>supervisor_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Supervisor Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,46 +791,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>date_prophets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Date of Prophets</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>date_joined</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Date Joined</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
+          <t>employee_number</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
+          <t>Employee Number</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>supervisor_phone</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>supervisor_phone</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>supervisor_email</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>supervisor_email</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date_prophets</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>date_prophets</t>
+          <t>Previous Department</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date_joined</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>date_joined</t>
+          <t>Previous Location</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,85 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>employee_number</t>
+          <t>job_title_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>employee_number</t>
+          <t>Job Title Before</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>department_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>location_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>job_title_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
